--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/MISSISSIPPI_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/MISSISSIPPI_2021.xlsx
@@ -1878,7 +1878,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C85">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C158">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C166">
@@ -10453,7 +10453,7 @@
         <v>21</v>
       </c>
       <c r="D561">
-        <v>0.009138381201044387</v>
+        <v>0.009138381201044389</v>
       </c>
     </row>
     <row r="562">
